--- a/ListasCh/public/lista-chequeo.xlsx
+++ b/ListasCh/public/lista-chequeo.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fernando T\Escritorio\PROGRAMACION\web3100\webapp-lista-chequeo(v2)\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64612A8F-03D7-4F6D-A57E-CCCB37C8DC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="19440" windowHeight="14880" tabRatio="894" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" tabRatio="894" firstSheet="8" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="TABLA DE CONTENIDO" sheetId="3" r:id="rId1"/>
@@ -26,13 +25,14 @@
     <sheet name="MODELO" sheetId="7" r:id="rId11"/>
     <sheet name="CAMBIO DIRECCION IPS" sheetId="12" r:id="rId12"/>
     <sheet name="PGRSA - RESIDUOS" sheetId="13" r:id="rId13"/>
+    <sheet name="APERTURA SEDE IPS" sheetId="14" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="313">
   <si>
     <t>Criterio</t>
   </si>
@@ -912,12 +912,72 @@
   </si>
   <si>
     <t>TT-GESTION INTEGRAL DE RESIDUOS - PGRSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Es exigible a edificaciones donde funcione el prestador, construidas, ampliadas o remodeladas con posterioridad al 2 de diciembre de 1996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Para prestadores ubicados en edificaciones de uso mixto construidas, ampliadas o remodeladas con posterioridad al 2 de diciembre de 1996, se solicitará el permiso otorgado por la propiedad horizontal para la adecuación en la edificación de servicios de salud, y la licencia de construcción de la edificación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Sólo será exigible a prestadores con servicios de urgencias, servicios de cirugía, o de unidad de cuidado intensivo neonatal, pediátrico, adulto, de acuerdo con lo establecido en la NSR 10 que funcionen en edificaciones construidas con anterioridad al 2010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Para prestadores que funcionen en edificaciones construidas con anterioridad a mayo del 2005, se solicitará una certificación expedida por un profesional competente en la cual certifique que las instalaciones eléctricas de la edificación donde se prestan los servicios de salud no representan alto riesgo para la salud y la vida de las personas y animales, o atenten contra el medio ambiente,  Adicionalmente el prestador deberá presentar un plan de ajustes de las instalaciones eléctricas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Para prestadores que funcionen en edificaciones construidas con posterioridad a mayo del 2005, o edificaciones adaptadas como instituciones de salud, se solicitará una certificación expedida por un organismo de inspección acreditado por la ONAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1  Formulario de Novedad </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2  Documento de Existencia y Representación Legal vigente, de la sede principal y la nueva sede </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3  En dicho certificado se deberá especificar la ubicación de la o las sedes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4  Declaración de la Autoevaluación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5  Copia del documento de identidad del representante legal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6  Copia de la licencia de construcción </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7  Certificado de seguridad de la edificación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8  Copia del estudio de vulnerabilidad estructural  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9  Copia del plan hospitalario para emergencias </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10  Copia del plan de mantenimiento de la planta física </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11  Formulario de Novedad </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12  Declaración de la Autoevaluación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13  Copia del documento de identificación del profesional independiente de salud </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14  Certificado de conformidad de las instalaciones eléctricas </t>
+  </si>
+  <si>
+    <t>TT-SOPORTES PARA APERTURA DE SEDE PARA IPS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1016,9 +1076,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1056,9 +1116,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1093,7 +1153,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1128,7 +1188,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1301,7 +1361,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1326,7 +1386,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{120A7DE4-046B-4BA2-95BF-F7472EE8C357}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1624,7 +1684,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA368CF3-524C-4931-89EF-545FE7F097D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1645,7 +1705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5C48067-A842-4EF3-82F9-6ABE699CC7AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1716,7 +1776,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C077E37-386A-4914-9CE8-AC35B091C99B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1936,8 +1996,129 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>297</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2078,7 +2259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2224,7 +2405,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FFBEEB-A428-47EC-959D-419D091935E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2319,7 +2500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99250AE1-865E-4D30-BA74-D77407B89584}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2415,7 +2596,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16520F0C-1B26-44F8-974E-86CCDF784754}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2836,7 +3017,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{548B6E16-CA28-4FC3-914D-820CCAE5BC94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3011,7 +3192,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83C2FCDF-D2ED-4696-9E83-3CBBB86B6AE3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3062,7 +3243,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23DD03EA-65E3-4EDE-AFEE-37F3D0661D30}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/ListasCh/public/lista-chequeo.xlsx
+++ b/ListasCh/public/lista-chequeo.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" tabRatio="894" firstSheet="8" activeTab="13"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" tabRatio="894" firstSheet="8" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="TABLA DE CONTENIDO" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="316">
   <si>
     <t>Criterio</t>
   </si>
@@ -920,9 +920,6 @@
     <t xml:space="preserve">  Para prestadores ubicados en edificaciones de uso mixto construidas, ampliadas o remodeladas con posterioridad al 2 de diciembre de 1996, se solicitará el permiso otorgado por la propiedad horizontal para la adecuación en la edificación de servicios de salud, y la licencia de construcción de la edificación</t>
   </si>
   <si>
-    <t xml:space="preserve">  Sólo será exigible a prestadores con servicios de urgencias, servicios de cirugía, o de unidad de cuidado intensivo neonatal, pediátrico, adulto, de acuerdo con lo establecido en la NSR 10 que funcionen en edificaciones construidas con anterioridad al 2010</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Para prestadores que funcionen en edificaciones construidas con anterioridad a mayo del 2005, se solicitará una certificación expedida por un profesional competente en la cual certifique que las instalaciones eléctricas de la edificación donde se prestan los servicios de salud no representan alto riesgo para la salud y la vida de las personas y animales, o atenten contra el medio ambiente,  Adicionalmente el prestador deberá presentar un plan de ajustes de las instalaciones eléctricas</t>
   </si>
   <si>
@@ -944,15 +941,9 @@
     <t xml:space="preserve">5  Copia del documento de identidad del representante legal </t>
   </si>
   <si>
-    <t xml:space="preserve">6  Copia de la licencia de construcción </t>
-  </si>
-  <si>
     <t xml:space="preserve">7  Certificado de seguridad de la edificación </t>
   </si>
   <si>
-    <t xml:space="preserve">8  Copia del estudio de vulnerabilidad estructural  </t>
-  </si>
-  <si>
     <t xml:space="preserve">9  Copia del plan hospitalario para emergencias </t>
   </si>
   <si>
@@ -968,10 +959,28 @@
     <t xml:space="preserve">13  Copia del documento de identificación del profesional independiente de salud </t>
   </si>
   <si>
-    <t xml:space="preserve">14  Certificado de conformidad de las instalaciones eléctricas </t>
-  </si>
-  <si>
     <t>TT-SOPORTES PARA APERTURA DE SEDE PARA IPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTT-6  Copia de la licencia de construcción </t>
+  </si>
+  <si>
+    <t>8  Copia del estudio de vulnerabilidad estructural, Sólo será exigible a prestadores con servicios de urgencias, servicios de cirugía, o de unidad de cuidado intensivo neonatal, pediátrico, adulto, de acuerdo con lo establecido en la NSR 10 que funcionen en edificaciones construidas con anterioridad al 2010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTT-14  Certificado de conformidad de las instalaciones eléctricas </t>
+  </si>
+  <si>
+    <t>1. OPCION 1</t>
+  </si>
+  <si>
+    <t>T-TITULO</t>
+  </si>
+  <si>
+    <t>TTT-OTRO CONCEPTO</t>
+  </si>
+  <si>
+    <t>TT-SUBTITULO</t>
   </si>
 </sst>
 </file>
@@ -1685,7 +1694,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1697,6 +1706,26 @@
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -1998,7 +2027,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2014,37 +2043,37 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2059,57 +2088,52 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>296</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>297</v>
       </c>
     </row>
   </sheetData>

--- a/ListasCh/public/lista-chequeo.xlsx
+++ b/ListasCh/public/lista-chequeo.xlsx
@@ -977,10 +977,10 @@
     <t>T-TITULO</t>
   </si>
   <si>
-    <t>TTT-OTRO CONCEPTO</t>
-  </si>
-  <si>
     <t>TT-SUBTITULO</t>
+  </si>
+  <si>
+    <t>T-Criterio con desglose</t>
   </si>
 </sst>
 </file>
@@ -1715,12 +1715,12 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">

--- a/ListasCh/public/lista-chequeo.xlsx
+++ b/ListasCh/public/lista-chequeo.xlsx
@@ -974,13 +974,13 @@
     <t>1. OPCION 1</t>
   </si>
   <si>
-    <t>T-TITULO</t>
-  </si>
-  <si>
     <t>TT-SUBTITULO</t>
   </si>
   <si>
     <t>T-Criterio con desglose</t>
+  </si>
+  <si>
+    <t>TTT-TITULO</t>
   </si>
 </sst>
 </file>
@@ -1710,17 +1710,17 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">

--- a/ListasCh/public/lista-chequeo.xlsx
+++ b/ListasCh/public/lista-chequeo.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" tabRatio="894" firstSheet="8" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" tabRatio="894" firstSheet="9" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="TABLA DE CONTENIDO" sheetId="3" r:id="rId1"/>
@@ -26,13 +26,14 @@
     <sheet name="CAMBIO DIRECCION IPS" sheetId="12" r:id="rId12"/>
     <sheet name="PGRSA - RESIDUOS" sheetId="13" r:id="rId13"/>
     <sheet name="APERTURA SEDE IPS" sheetId="14" r:id="rId14"/>
+    <sheet name="CIERRE DE SEDE" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="321">
   <si>
     <t>Criterio</t>
   </si>
@@ -981,6 +982,31 @@
   </si>
   <si>
     <t>TTT-TITULO</t>
+  </si>
+  <si>
+    <t>TTT-CIERRE DE SEDE</t>
+  </si>
+  <si>
+    <t>TT-Documentación para Cierre de Sede</t>
+  </si>
+  <si>
+    <t>2. Documento de Existencia y Representación Legal vigente, de acuerdo al tipo de entidad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Carta del 
+prestador dirigida al 
+ente territorial donde 
+se informa sobre la 
+gestión adelantada 
+con las Historias 
+Clínicas y su entrega 
+final. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Copia del 
+documento de 
+identidad del 
+representante legal. </t>
   </si>
 </sst>
 </file>
@@ -1048,7 +1074,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1067,6 +1093,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2141,6 +2168,62 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>320</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C24"/>

--- a/ListasCh/public/lista-chequeo.xlsx
+++ b/ListasCh/public/lista-chequeo.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" tabRatio="894" firstSheet="9" activeTab="14"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" tabRatio="894" firstSheet="9" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="TABLA DE CONTENIDO" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="319">
   <si>
     <t>Criterio</t>
   </si>
@@ -915,18 +915,6 @@
     <t>TT-GESTION INTEGRAL DE RESIDUOS - PGRSA</t>
   </si>
   <si>
-    <t xml:space="preserve">  Es exigible a edificaciones donde funcione el prestador, construidas, ampliadas o remodeladas con posterioridad al 2 de diciembre de 1996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Para prestadores ubicados en edificaciones de uso mixto construidas, ampliadas o remodeladas con posterioridad al 2 de diciembre de 1996, se solicitará el permiso otorgado por la propiedad horizontal para la adecuación en la edificación de servicios de salud, y la licencia de construcción de la edificación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Para prestadores que funcionen en edificaciones construidas con anterioridad a mayo del 2005, se solicitará una certificación expedida por un profesional competente en la cual certifique que las instalaciones eléctricas de la edificación donde se prestan los servicios de salud no representan alto riesgo para la salud y la vida de las personas y animales, o atenten contra el medio ambiente,  Adicionalmente el prestador deberá presentar un plan de ajustes de las instalaciones eléctricas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Para prestadores que funcionen en edificaciones construidas con posterioridad a mayo del 2005, o edificaciones adaptadas como instituciones de salud, se solicitará una certificación expedida por un organismo de inspección acreditado por la ONAC</t>
-  </si>
-  <si>
     <t xml:space="preserve">1  Formulario de Novedad </t>
   </si>
   <si>
@@ -954,22 +942,10 @@
     <t xml:space="preserve">11  Formulario de Novedad </t>
   </si>
   <si>
-    <t xml:space="preserve">12  Declaración de la Autoevaluación </t>
-  </si>
-  <si>
-    <t xml:space="preserve">13  Copia del documento de identificación del profesional independiente de salud </t>
-  </si>
-  <si>
     <t>TT-SOPORTES PARA APERTURA DE SEDE PARA IPS</t>
   </si>
   <si>
-    <t xml:space="preserve">TTT-6  Copia de la licencia de construcción </t>
-  </si>
-  <si>
     <t>8  Copia del estudio de vulnerabilidad estructural, Sólo será exigible a prestadores con servicios de urgencias, servicios de cirugía, o de unidad de cuidado intensivo neonatal, pediátrico, adulto, de acuerdo con lo establecido en la NSR 10 que funcionen en edificaciones construidas con anterioridad al 2010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTT-14  Certificado de conformidad de las instalaciones eléctricas </t>
   </si>
   <si>
     <t>1. OPCION 1</t>
@@ -1007,6 +983,24 @@
 documento de 
 identidad del 
 representante legal. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6  Copia de la licencia de construcción </t>
+  </si>
+  <si>
+    <t>TTT-  Es exigible a edificaciones donde funcione el prestador, construidas, ampliadas o remodeladas con posterioridad al 2 de diciembre de 1996</t>
+  </si>
+  <si>
+    <t>TTT-  Para prestadores ubicados en edificaciones de uso mixto construidas, ampliadas o remodeladas con posterioridad al 2 de diciembre de 1996, se solicitará el permiso otorgado por la propiedad horizontal para la adecuación en la edificación de servicios de salud, y la licencia de construcción de la edificación</t>
+  </si>
+  <si>
+    <t>TTT-  Para prestadores que funcionen en edificaciones construidas con anterioridad a mayo del 2005, se solicitará una certificación expedida por un profesional competente en la cual certifique que las instalaciones eléctricas de la edificación donde se prestan los servicios de salud no representan alto riesgo para la salud y la vida de las personas y animales, o atenten contra el medio ambiente,  Adicionalmente el prestador deberá presentar un plan de ajustes de las instalaciones eléctricas</t>
+  </si>
+  <si>
+    <t>TTT-  Para prestadores que funcionen en edificaciones construidas con posterioridad a mayo del 2005, o edificaciones adaptadas como instituciones de salud, se solicitará una certificación expedida por un organismo de inspección acreditado por la ONAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14  Certificado de conformidad de las instalaciones eléctricas </t>
   </si>
 </sst>
 </file>
@@ -1737,22 +1731,22 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -2054,7 +2048,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2070,97 +2064,87 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -2186,17 +2170,17 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2206,17 +2190,17 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/ListasCh/public/lista-chequeo.xlsx
+++ b/ListasCh/public/lista-chequeo.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="318">
   <si>
     <t>Criterio</t>
   </si>
@@ -918,34 +918,7 @@
     <t xml:space="preserve">1  Formulario de Novedad </t>
   </si>
   <si>
-    <t xml:space="preserve">2  Documento de Existencia y Representación Legal vigente, de la sede principal y la nueva sede </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3  En dicho certificado se deberá especificar la ubicación de la o las sedes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4  Declaración de la Autoevaluación </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5  Copia del documento de identidad del representante legal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7  Certificado de seguridad de la edificación </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9  Copia del plan hospitalario para emergencias </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10  Copia del plan de mantenimiento de la planta física </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11  Formulario de Novedad </t>
-  </si>
-  <si>
     <t>TT-SOPORTES PARA APERTURA DE SEDE PARA IPS</t>
-  </si>
-  <si>
-    <t>8  Copia del estudio de vulnerabilidad estructural, Sólo será exigible a prestadores con servicios de urgencias, servicios de cirugía, o de unidad de cuidado intensivo neonatal, pediátrico, adulto, de acuerdo con lo establecido en la NSR 10 que funcionen en edificaciones construidas con anterioridad al 2010</t>
   </si>
   <si>
     <t>1. OPCION 1</t>
@@ -985,9 +958,6 @@
 representante legal. </t>
   </si>
   <si>
-    <t xml:space="preserve">6  Copia de la licencia de construcción </t>
-  </si>
-  <si>
     <t>TTT-  Es exigible a edificaciones donde funcione el prestador, construidas, ampliadas o remodeladas con posterioridad al 2 de diciembre de 1996</t>
   </si>
   <si>
@@ -1000,7 +970,34 @@
     <t>TTT-  Para prestadores que funcionen en edificaciones construidas con posterioridad a mayo del 2005, o edificaciones adaptadas como instituciones de salud, se solicitará una certificación expedida por un organismo de inspección acreditado por la ONAC</t>
   </si>
   <si>
-    <t xml:space="preserve">14  Certificado de conformidad de las instalaciones eléctricas </t>
+    <t>2  Documento de Existencia y Representación Legal vigente, de la sede principal y la nueva sede (En dicho certificado se deberá especificar la ubicación de la o las sedes )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3  Declaración de la Autoevaluación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4  Copia del documento de identidad del representante legal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5  Copia de la licencia de construcción </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6  Certificado de seguridad de la edificación </t>
+  </si>
+  <si>
+    <t>7  Copia del estudio de vulnerabilidad estructural, Sólo será exigible a prestadores con servicios de urgencias, servicios de cirugía, o de unidad de cuidado intensivo neonatal, pediátrico, adulto, de acuerdo con lo establecido en la NSR 10 que funcionen en edificaciones construidas con anterioridad al 2010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8  Copia del plan hospitalario para emergencias </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9  Copia del plan de mantenimiento de la planta física </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10  Formulario de Novedad </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11  Certificado de conformidad de las instalaciones eléctricas </t>
   </si>
 </sst>
 </file>
@@ -1731,22 +1728,22 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -2048,7 +2045,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2064,7 +2061,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2074,77 +2071,72 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -2170,17 +2162,17 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2190,17 +2182,17 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/ListasCh/public/lista-chequeo.xlsx
+++ b/ListasCh/public/lista-chequeo.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="317">
   <si>
     <t>Criterio</t>
   </si>
@@ -913,9 +913,6 @@
   </si>
   <si>
     <t>TT-GESTION INTEGRAL DE RESIDUOS - PGRSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1  Formulario de Novedad </t>
   </si>
   <si>
     <t>TT-SOPORTES PARA APERTURA DE SEDE PARA IPS</t>
@@ -970,34 +967,34 @@
     <t>TTT-  Para prestadores que funcionen en edificaciones construidas con posterioridad a mayo del 2005, o edificaciones adaptadas como instituciones de salud, se solicitará una certificación expedida por un organismo de inspección acreditado por la ONAC</t>
   </si>
   <si>
-    <t>2  Documento de Existencia y Representación Legal vigente, de la sede principal y la nueva sede (En dicho certificado se deberá especificar la ubicación de la o las sedes )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3  Declaración de la Autoevaluación </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4  Copia del documento de identidad del representante legal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5  Copia de la licencia de construcción </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6  Certificado de seguridad de la edificación </t>
-  </si>
-  <si>
-    <t>7  Copia del estudio de vulnerabilidad estructural, Sólo será exigible a prestadores con servicios de urgencias, servicios de cirugía, o de unidad de cuidado intensivo neonatal, pediátrico, adulto, de acuerdo con lo establecido en la NSR 10 que funcionen en edificaciones construidas con anterioridad al 2010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8  Copia del plan hospitalario para emergencias </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9  Copia del plan de mantenimiento de la planta física </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10  Formulario de Novedad </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11  Certificado de conformidad de las instalaciones eléctricas </t>
+    <t>1  Documento de Existencia y Representación Legal vigente, de la sede principal y la nueva sede (En dicho certificado se deberá especificar la ubicación de la o las sedes )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2  Copia del documento de identidad del representante legal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3  Copia de la licencia de construcción </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4  Certificado de seguridad de la edificación </t>
+  </si>
+  <si>
+    <t>5  Copia del estudio de vulnerabilidad estructural, Sólo será exigible a prestadores con servicios de urgencias, servicios de cirugía, o de unidad de cuidado intensivo neonatal, pediátrico, adulto, de acuerdo con lo establecido en la NSR 10 que funcionen en edificaciones construidas con anterioridad al 2010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6  Copia del plan hospitalario para emergencias </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7  Copia del plan de mantenimiento de la planta física </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8  Certificado de conformidad de las instalaciones eléctricas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9  Formulario de Novedad </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10  Declaración de la Autoevaluación </t>
   </si>
 </sst>
 </file>
@@ -1728,22 +1725,22 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -2045,7 +2042,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2061,12 +2058,12 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2081,22 +2078,22 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2116,27 +2113,22 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -2162,17 +2154,17 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2182,17 +2174,17 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
